--- a/E-Commerce(Team-4).xlsx
+++ b/E-Commerce(Team-4).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\307448\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F174A4DC-35E3-4480-A01B-20B184A5D7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DCFCABF-AC15-4989-8132-F4F06C71E2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3812113D-01BE-456C-B2BA-2B3A9177243A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="161">
   <si>
     <r>
       <rPr>
@@ -77,13 +77,687 @@
   </si>
   <si>
     <t xml:space="preserve">                                                   NOTES</t>
+  </si>
+  <si>
+    <t>Pod CrashLoopBackOff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Container keeps restarting due to wrong port or missing env vars</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Checked logs using </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>kubectl logs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, fixed port &amp; env configuration</t>
+    </r>
+  </si>
+  <si>
+    <t>Review Service</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Very common during initial deployment</t>
+  </si>
+  <si>
+    <t>Service-Pod Label Mismatch</t>
+  </si>
+  <si>
+    <t>Service not routing traffic to pods</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Matched </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>selector</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> labels with pod </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>labels</t>
+    </r>
+  </si>
+  <si>
+    <t>No endpoints created if mismatch</t>
+  </si>
+  <si>
+    <t>ImagePullBackOff</t>
+  </si>
+  <si>
+    <t>Kubernetes unable to pull Docker image</t>
+  </si>
+  <si>
+    <t>Verified image name/tag, added imagePullSecrets for private repo</t>
+  </si>
+  <si>
+    <t>All Services</t>
+  </si>
+  <si>
+    <t>Happens with private DockerHub images</t>
+  </si>
+  <si>
+    <t>Missing Environment Variables</t>
+  </si>
+  <si>
+    <t>Application crashes due to missing configs</t>
+  </si>
+  <si>
+    <t>Added correct env variables in Deployment YAML</t>
+  </si>
+  <si>
+    <t>Ensure naming matches application code</t>
+  </si>
+  <si>
+    <t>ConfigMap Mount Failure</t>
+  </si>
+  <si>
+    <t>Config files not accessible inside container</t>
+  </si>
+  <si>
+    <t>Fixed volume and volumeMount name mismatch</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Small typo causes major issue</t>
+  </si>
+  <si>
+    <t>Database Connection Failure</t>
+  </si>
+  <si>
+    <t>App unable to connect to DB using localhost</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Replaced </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>localhost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with Kubernetes service name</t>
+    </r>
+  </si>
+  <si>
+    <t>Database / Review Service</t>
+  </si>
+  <si>
+    <t>Kubernetes networking concept issue</t>
+  </si>
+  <si>
+    <t>Incorrect Service Type</t>
+  </si>
+  <si>
+    <t>Application not accessible externally</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Changed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ClusterIP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>NodePort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>LoadBalancer</t>
+    </r>
+  </si>
+  <si>
+    <t>Depends on environment (local/cloud)</t>
+  </si>
+  <si>
+    <t>Liveness/Readiness Probe Failure</t>
+  </si>
+  <si>
+    <t>Pod restarting even when app is fine</t>
+  </si>
+  <si>
+    <t>Corrected health endpoint &amp; added delay</t>
+  </si>
+  <si>
+    <t>Avoid aggressive probes</t>
+  </si>
+  <si>
+    <t>Resource Limit Exceeded</t>
+  </si>
+  <si>
+    <t>Pod killed due to insufficient memory</t>
+  </si>
+  <si>
+    <t>Increased memory/CPU limits in YAML</t>
+  </si>
+  <si>
+    <t>Causes OOMKilled errors</t>
+  </si>
+  <si>
+    <t>Ingress Misconfiguration</t>
+  </si>
+  <si>
+    <t>External routing not working</t>
+  </si>
+  <si>
+    <t>Fixed host/path rules &amp; ensured ingress controller installed</t>
+  </si>
+  <si>
+    <t>API Gateway / Review Service</t>
+  </si>
+  <si>
+    <t>Often missed step</t>
+  </si>
+  <si>
+    <t>Namespace Miscommunication</t>
+  </si>
+  <si>
+    <t>Services unable to communicate across namespaces</t>
+  </si>
+  <si>
+    <t>Used same namespace or full DNS naming</t>
+  </si>
+  <si>
+    <t>Important in multi-service apps</t>
+  </si>
+  <si>
+    <t>YAML Indentation Errors</t>
+  </si>
+  <si>
+    <t>Deployment behaves incorrectly or fails silently</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Validated YAML using lint tools (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>kubectl apply --dry-run</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>YAML is whitespace-sensitive</t>
+  </si>
+  <si>
+    <t>Hardcoded URLs</t>
+  </si>
+  <si>
+    <t>Service fails in cluster environment</t>
+  </si>
+  <si>
+    <t>Replaced with service-based DNS names</t>
+  </si>
+  <si>
+    <t>Avoid localhost in microservices</t>
+  </si>
+  <si>
+    <t>DB Initialization Race Condition</t>
+  </si>
+  <si>
+    <t>App starts before DB is ready</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Added </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>initContainers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or retry logic</t>
+    </r>
+  </si>
+  <si>
+    <t>Common in microservices startup</t>
+  </si>
+  <si>
+    <t>Scaling Issues</t>
+  </si>
+  <si>
+    <t>Multiple replicas causing inconsistent behavior</t>
+  </si>
+  <si>
+    <t>Ensured stateless design &amp; DB connection pooling</t>
+  </si>
+  <si>
+    <t>Appears during scaling</t>
+  </si>
+  <si>
+    <t>Secret Misconfiguration</t>
+  </si>
+  <si>
+    <t>Sensitive data not injected properly</t>
+  </si>
+  <si>
+    <t>Used Kubernetes Secrets correctly with env or volume</t>
+  </si>
+  <si>
+    <t>Critical for security</t>
+  </si>
+  <si>
+    <t>Port Mismatch</t>
+  </si>
+  <si>
+    <t>Container port differs from service targetPort</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Aligned </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>containerPort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>targetPort</t>
+    </r>
+  </si>
+  <si>
+    <t>Breaks service routing</t>
+  </si>
+  <si>
+    <t>Incorrect Volume Mount Path</t>
+  </si>
+  <si>
+    <t>Application cannot find required files</t>
+  </si>
+  <si>
+    <t>Fixed mount path to match application expectation</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Use </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>nslookup</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> inside pod</t>
+    </r>
+  </si>
+  <si>
+    <t>DNS Resolution Failure</t>
+  </si>
+  <si>
+    <t>Service name not resolving inside cluster</t>
+  </si>
+  <si>
+    <t>Verified service name and namespace</t>
+  </si>
+  <si>
+    <t>Deployment Not Updating</t>
+  </si>
+  <si>
+    <t>Changes not reflected after apply</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Used </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>kubectl rollout restart deployment</t>
+    </r>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Happens due to image caching</t>
+  </si>
+  <si>
+    <t>HAProxy 503 Error</t>
+  </si>
+  <si>
+    <t>503 Service Unavailable from HAProxy</t>
+  </si>
+  <si>
+    <t>Occurs when backend has no healthy endpoints</t>
+  </si>
+  <si>
+    <t>No Healthy Upstream (Envoy)</t>
+  </si>
+  <si>
+    <t>KGateway returning "no healthy upstream</t>
+  </si>
+  <si>
+    <t>Fixed HTTPRoute path and ensured backend service is correctly mapped</t>
+  </si>
+  <si>
+    <t>API Gateway / HAProx</t>
+  </si>
+  <si>
+    <t>Verified backend NodePort and ensured service endpoints are available</t>
+  </si>
+  <si>
+    <t>Service Has No Endpoints</t>
+  </si>
+  <si>
+    <t>Service shows empty endpoints</t>
+  </si>
+  <si>
+    <t>Fixed readiness probe and ensured pods become Ready                                                                                                      API Gateway High</t>
+  </si>
+  <si>
+    <t>Blocks service traffic even if pod is running</t>
+  </si>
+  <si>
+    <t>API Gateway</t>
+  </si>
+  <si>
+    <t>Service won’t route traffic without endpoints</t>
+  </si>
+  <si>
+    <t>Common when route does not match request path</t>
+  </si>
+  <si>
+    <t>Readiness Probe Failure</t>
+  </si>
+  <si>
+    <t>Pod running but not Ready (0/1)</t>
+  </si>
+  <si>
+    <t>Corrected probe port from 3000 to 3012</t>
+  </si>
+  <si>
+    <t>Liveness Probe Failure</t>
+  </si>
+  <si>
+    <t>Container restarting due to failed health checks</t>
+  </si>
+  <si>
+    <t>Updated health endpoint and correct port</t>
+  </si>
+  <si>
+    <t>Causes continuous restarts</t>
+  </si>
+  <si>
+    <t>Application running on different port than service/probes</t>
+  </si>
+  <si>
+    <t>Aligned containerPort, targetPort, and probe ports</t>
+  </si>
+  <si>
+    <t>Very common misconfiguration</t>
+  </si>
+  <si>
+    <t>Frontend CrashLoopBackOff</t>
+  </si>
+  <si>
+    <t>Nginx failed due to wrong upstream name</t>
+  </si>
+  <si>
+    <t>Updated upstream from "api-gateway" to correct service name</t>
+  </si>
+  <si>
+    <t>Frontend UI</t>
+  </si>
+  <si>
+    <t>DNS/service name must match exactly</t>
+  </si>
+  <si>
+    <t>host not found in upstream" error</t>
+  </si>
+  <si>
+    <t>Used correct Kubernetes service name (clahanstore-gateway)</t>
+  </si>
+  <si>
+    <t>Frontend UI </t>
+  </si>
+  <si>
+    <t>K8s DNS naming issue</t>
+  </si>
+  <si>
+    <t>Mixing Gateways</t>
+  </si>
+  <si>
+    <t>Used both api-gateway and KGateway together</t>
+  </si>
+  <si>
+    <t>Chose single gateway approach and removed unused configs</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>Causes routing conflicts and confusion</t>
+  </si>
+  <si>
+    <t>Wrong HAProxy Backend</t>
+  </si>
+  <si>
+    <t>HAProxy pointing to wrong NodePort (KGateway instead of API Gateway)</t>
+  </si>
+  <si>
+    <t>Updated HAProxy backend to correct NodePort</t>
+  </si>
+  <si>
+    <t>HAProxy</t>
+  </si>
+  <si>
+    <t>Traffic routed to wrong component</t>
+  </si>
+  <si>
+    <t>HTTPRoute Path Mismatch</t>
+  </si>
+  <si>
+    <t>Request path not matching HTTPRoute definition</t>
+  </si>
+  <si>
+    <t>Updated HTTPRoute to include correct path (/recommendation)</t>
+  </si>
+  <si>
+    <t>KGateway</t>
+  </si>
+  <si>
+    <t>Must match exact request path</t>
+  </si>
+  <si>
+    <t>ClusterIP Not Exposed</t>
+  </si>
+  <si>
+    <t>Service not accessible externally</t>
+  </si>
+  <si>
+    <t>Changed service type to NodePort for HAProxy access</t>
+  </si>
+  <si>
+    <t>Medium </t>
+  </si>
+  <si>
+    <t>Required in non-cloud environments</t>
+  </si>
+  <si>
+    <t>LoadBalancer Pending</t>
+  </si>
+  <si>
+    <t>EXTERNAL-IP stuck in &lt;pending&gt; </t>
+  </si>
+  <si>
+    <t>Used HAProxy + NodePort as workaround</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Common without cloud controller</t>
+  </si>
+  <si>
+    <t>Git Pull Conflict</t>
+  </si>
+  <si>
+    <t>Local changes blocking git pul</t>
+  </si>
+  <si>
+    <t>Used git stash / commit before pulling updates</t>
+  </si>
+  <si>
+    <t>Git Workflow</t>
+  </si>
+  <si>
+    <t>Standard Git issue</t>
+  </si>
+  <si>
+    <t>Service Port Name Missing</t>
+  </si>
+  <si>
+    <t>Kubernetes validation error for service</t>
+  </si>
+  <si>
+    <t>Added name field in service port definition</t>
+  </si>
+  <si>
+    <t>Required for some K8s versions</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,6 +772,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -120,9 +799,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,19 +1139,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A312DD2B-5DEB-4FED-B72B-AE3CDEA92784}">
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="27.36328125" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" customWidth="1"/>
     <col min="3" max="3" width="62.36328125" customWidth="1"/>
-    <col min="4" max="4" width="52.453125" customWidth="1"/>
+    <col min="4" max="4" width="81.26953125" customWidth="1"/>
     <col min="5" max="5" width="32.6328125" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="43.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -490,6 +1172,808 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" t="s">
+        <v>99</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26" t="s">
+        <v>113</v>
+      </c>
+      <c r="E26" t="s">
+        <v>105</v>
+      </c>
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" t="s">
+        <v>115</v>
+      </c>
+      <c r="D27" t="s">
+        <v>116</v>
+      </c>
+      <c r="E27" t="s">
+        <v>105</v>
+      </c>
+      <c r="F27" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" t="s">
+        <v>120</v>
+      </c>
+      <c r="E28" t="s">
+        <v>121</v>
+      </c>
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>29</v>
+      </c>
+      <c r="B29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E29" t="s">
+        <v>125</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" t="s">
+        <v>130</v>
+      </c>
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C31" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" t="s">
+        <v>135</v>
+      </c>
+      <c r="F31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" t="s">
+        <v>140</v>
+      </c>
+      <c r="F32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" t="s">
+        <v>143</v>
+      </c>
+      <c r="D33" t="s">
+        <v>144</v>
+      </c>
+      <c r="E33" t="s">
+        <v>105</v>
+      </c>
+      <c r="F33" t="s">
+        <v>145</v>
+      </c>
+      <c r="G33" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" t="s">
+        <v>148</v>
+      </c>
+      <c r="D34" t="s">
+        <v>149</v>
+      </c>
+      <c r="E34" t="s">
+        <v>150</v>
+      </c>
+      <c r="F34" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>152</v>
+      </c>
+      <c r="C35" t="s">
+        <v>153</v>
+      </c>
+      <c r="D35" t="s">
+        <v>154</v>
+      </c>
+      <c r="E35" t="s">
+        <v>155</v>
+      </c>
+      <c r="F35" t="s">
+        <v>91</v>
+      </c>
+      <c r="G35" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>157</v>
+      </c>
+      <c r="C36" t="s">
+        <v>158</v>
+      </c>
+      <c r="D36" t="s">
+        <v>159</v>
+      </c>
+      <c r="E36" t="s">
+        <v>105</v>
+      </c>
+      <c r="F36" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
